--- a/tools/importer/reports/import-about-us.report.xlsx
+++ b/tools/importer/reports/import-about-us.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="51">
   <si>
     <t>_reportFile</t>
   </si>
@@ -37,25 +37,133 @@
     <t>url</t>
   </si>
   <si>
-    <t>about-us.report.json</t>
-  </si>
-  <si>
-    <t>["columns-media","columns-media","cards-gallery","tabs-profiles","cards-article","accordion-faq","hero-overlay"]</t>
+    <t>us/en.report.json</t>
+  </si>
+  <si>
+    <t>["hero-carousel","columns-featured","cards-adventures","cards-adventures","hero-feature"]</t>
+  </si>
+  <si>
+    <t>us/en</t>
+  </si>
+  <si>
+    <t>success</t>
+  </si>
+  <si>
+    <t>home</t>
+  </si>
+  <si>
+    <t>2026-09-05T17:53:42.665Z</t>
+  </si>
+  <si>
+    <t>WKND Adventures and Travel</t>
+  </si>
+  <si>
+    <t>https://wknd.site/us/en.html</t>
+  </si>
+  <si>
+    <t>us/en/about-us.report.json</t>
+  </si>
+  <si>
+    <t>["cards-contributor","cards-contributor"]</t>
+  </si>
+  <si>
+    <t>us/en/about-us</t>
   </si>
   <si>
     <t>about-us</t>
   </si>
   <si>
-    <t>success</t>
-  </si>
-  <si>
-    <t>2026-09-02T17:47:12.014Z</t>
-  </si>
-  <si>
-    <t>WKND Trendsetters - Fresh Looks, Bold Stories, Real Life</t>
-  </si>
-  <si>
-    <t>https://wknd-trendsetters.site/about-us</t>
+    <t>2026-09-05T18:24:35.468Z</t>
+  </si>
+  <si>
+    <t>About Us</t>
+  </si>
+  <si>
+    <t>https://wknd.site/us/en/about-us.html</t>
+  </si>
+  <si>
+    <t>us/en/adventures.report.json</t>
+  </si>
+  <si>
+    <t>["hero-feature","cards-adventures"]</t>
+  </si>
+  <si>
+    <t>us/en/adventures</t>
+  </si>
+  <si>
+    <t>adventures-2</t>
+  </si>
+  <si>
+    <t>2026-09-05T18:24:19.156Z</t>
+  </si>
+  <si>
+    <t>Adventures</t>
+  </si>
+  <si>
+    <t>https://wknd.site/us/en/adventures.html</t>
+  </si>
+  <si>
+    <t>us/en/faqs.report.json</t>
+  </si>
+  <si>
+    <t>["accordion-faq"]</t>
+  </si>
+  <si>
+    <t>us/en/faqs</t>
+  </si>
+  <si>
+    <t>faqs</t>
+  </si>
+  <si>
+    <t>2026-09-05T18:24:13.133Z</t>
+  </si>
+  <si>
+    <t>FAQs</t>
+  </si>
+  <si>
+    <t>https://wknd.site/us/en/faqs.html</t>
+  </si>
+  <si>
+    <t>us/en/adventures/climbing-new-zealand.report.json</t>
+  </si>
+  <si>
+    <t>["hero-carousel","columns-details","tabs-content"]</t>
+  </si>
+  <si>
+    <t>us/en/adventures/climbing-new-zealand</t>
+  </si>
+  <si>
+    <t>adventures</t>
+  </si>
+  <si>
+    <t>2026-09-05T18:24:24.455Z</t>
+  </si>
+  <si>
+    <t>Climbing New Zealand</t>
+  </si>
+  <si>
+    <t>https://wknd.site/us/en/adventures/climbing-new-zealand.html</t>
+  </si>
+  <si>
+    <t>us/en/magazine/arctic-surfing.report.json</t>
+  </si>
+  <si>
+    <t>["columns-byline","cards-upnext"]</t>
+  </si>
+  <si>
+    <t>us/en/magazine/arctic-surfing</t>
+  </si>
+  <si>
+    <t>magazine</t>
+  </si>
+  <si>
+    <t>2026-09-05T18:24:29.653Z</t>
+  </si>
+  <si>
+    <t>Arctic Surfing</t>
+  </si>
+  <si>
+    <t>https://wknd.site/us/en/magazine/arctic-surfing.html</t>
   </si>
 </sst>
 </file>
@@ -444,16 +552,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="2" width="50" customWidth="1"/>
-    <col min="3" max="3" width="10" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="1" max="2" width="50" customWidth="1"/>
+    <col min="3" max="3" width="39" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="7" width="50" customWidth="1"/>
-    <col min="8" max="8" width="41" customWidth="1"/>
+    <col min="7" max="7" width="28" customWidth="1"/>
+    <col min="8" max="8" width="50" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -496,16 +603,146 @@
         <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H2" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F6" t="s">
+        <v>41</v>
+      </c>
+      <c r="G6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" t="s">
+        <v>48</v>
+      </c>
+      <c r="G7" t="s">
+        <v>49</v>
+      </c>
+      <c r="H7" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
